--- a/2022 data/excel_outputs/402_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/402_boothwise_data.xlsx
@@ -14,11 +14,71 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="372">
   <si>
     <t>AC 402 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -376,7 +436,7 @@
     <t>UCHCH PRA. PA.PIPRA JUGAIL ROOM NO.2</t>
   </si>
   <si>
-    <t>UCHCH PRA. PA.PIPRA JUGAIL ROOM NO.■</t>
+    <t>CHTAPAUMTAL TAPAKALAMSAMLAM THAPASASAP TVAVAU CHAV2</t>
   </si>
   <si>
     <t>PRA.VI. GARDA TOLA JUGAIL</t>
@@ -1076,8 +1136,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1093,7 +1161,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1101,12 +1169,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1405,73 +1491,133 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="D2" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="E2" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="F2" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="G2" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="H2" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="I2" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="J2" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="K2" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="L2" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="M2" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="N2" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="O2" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="P2" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="Q2" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="R2" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="S2" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="T2" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="U2" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -1479,7 +1625,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C3">
         <v>1206</v>
@@ -1544,7 +1690,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C4">
         <v>1041</v>
@@ -1609,7 +1755,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>1108</v>
@@ -1674,7 +1820,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C6">
         <v>1041</v>
@@ -1739,7 +1885,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>1015</v>
@@ -1804,7 +1950,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>1054</v>
@@ -1869,7 +2015,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C9">
         <v>938</v>
@@ -1934,7 +2080,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C10">
         <v>606</v>
@@ -1999,7 +2145,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C11">
         <v>871</v>
@@ -2064,7 +2210,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C12">
         <v>918</v>
@@ -2129,7 +2275,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C13">
         <v>1041</v>
@@ -2194,7 +2340,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C14">
         <v>1124</v>
@@ -2259,7 +2405,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="C15">
         <v>1160</v>
@@ -2324,7 +2470,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C16">
         <v>1020</v>
@@ -2389,7 +2535,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C17">
         <v>907</v>
@@ -2454,7 +2600,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C18">
         <v>1156</v>
@@ -2519,7 +2665,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C19">
         <v>507</v>
@@ -2584,7 +2730,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C20">
         <v>603</v>
@@ -2649,7 +2795,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C21">
         <v>360</v>
@@ -2714,7 +2860,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C22">
         <v>1195</v>
@@ -2779,7 +2925,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C23">
         <v>969</v>
@@ -2844,7 +2990,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="C24">
         <v>1181</v>
@@ -2909,7 +3055,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C25">
         <v>848</v>
@@ -2974,7 +3120,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C26">
         <v>1106</v>
@@ -3039,7 +3185,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C27">
         <v>1182</v>
@@ -3104,7 +3250,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C28">
         <v>800</v>
@@ -3169,7 +3315,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="C29">
         <v>822</v>
@@ -3234,7 +3380,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C30">
         <v>741</v>
@@ -3299,7 +3445,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C31">
         <v>723</v>
@@ -3364,7 +3510,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C32">
         <v>989</v>
@@ -3429,7 +3575,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C33">
         <v>1138</v>
@@ -3494,7 +3640,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="C34">
         <v>780</v>
@@ -3559,7 +3705,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="C35">
         <v>761</v>
@@ -3624,7 +3770,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C36">
         <v>984</v>
@@ -3689,7 +3835,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C37">
         <v>706</v>
@@ -3754,7 +3900,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C38">
         <v>578</v>
@@ -3819,7 +3965,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C39">
         <v>735</v>
@@ -3884,7 +4030,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C40">
         <v>496</v>
@@ -3949,7 +4095,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="C41">
         <v>1097</v>
@@ -4014,7 +4160,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="C42">
         <v>670</v>
@@ -4079,7 +4225,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="C43">
         <v>545</v>
@@ -4144,7 +4290,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C44">
         <v>754</v>
@@ -4209,7 +4355,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C45">
         <v>726</v>
@@ -4274,7 +4420,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C46">
         <v>762</v>
@@ -4339,7 +4485,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C47">
         <v>647</v>
@@ -4404,7 +4550,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="C48">
         <v>565</v>
@@ -4469,7 +4615,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C49">
         <v>332</v>
@@ -4534,7 +4680,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="C50">
         <v>984</v>
@@ -4599,7 +4745,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C51">
         <v>659</v>
@@ -4664,7 +4810,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="C52">
         <v>692</v>
@@ -4729,7 +4875,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C53">
         <v>696</v>
@@ -4794,7 +4940,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="C54">
         <v>713</v>
@@ -4859,7 +5005,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="C55">
         <v>1141</v>
@@ -4924,7 +5070,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C56">
         <v>1104</v>
@@ -4989,7 +5135,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="C57">
         <v>1175</v>
@@ -5054,7 +5200,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="C58">
         <v>1056</v>
@@ -5119,7 +5265,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="C59">
         <v>995</v>
@@ -5184,7 +5330,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="C60">
         <v>1126</v>
@@ -5249,7 +5395,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C61">
         <v>1044</v>
@@ -5314,7 +5460,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="C62">
         <v>1189</v>
@@ -5379,7 +5525,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C63">
         <v>1055</v>
@@ -5444,7 +5590,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="C64">
         <v>1140</v>
@@ -5509,7 +5655,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="C65">
         <v>1137</v>
@@ -5574,7 +5720,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C66">
         <v>1211</v>
@@ -5639,7 +5785,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="C67">
         <v>1063</v>
@@ -5704,7 +5850,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="C68">
         <v>1192</v>
@@ -5769,7 +5915,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="C69">
         <v>1063</v>
@@ -5834,7 +5980,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="C70">
         <v>707</v>
@@ -5899,7 +6045,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="C71">
         <v>805</v>
@@ -5964,7 +6110,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C72">
         <v>1053</v>
@@ -6029,7 +6175,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="C73">
         <v>1067</v>
@@ -6094,7 +6240,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="C74">
         <v>996</v>
@@ -6159,7 +6305,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="C75">
         <v>983</v>
@@ -6224,7 +6370,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C76">
         <v>1013</v>
@@ -6289,7 +6435,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C77">
         <v>713</v>
@@ -6354,7 +6500,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="C78">
         <v>626</v>
@@ -6419,7 +6565,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C79">
         <v>1109</v>
@@ -6484,7 +6630,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C80">
         <v>605</v>
@@ -6549,7 +6695,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="C81">
         <v>609</v>
@@ -6614,7 +6760,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="C82">
         <v>1087</v>
@@ -6679,7 +6825,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="C83">
         <v>729</v>
@@ -6744,7 +6890,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="C84">
         <v>780</v>
@@ -6809,7 +6955,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C85">
         <v>1085</v>
@@ -6874,7 +7020,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C86">
         <v>1228</v>
@@ -6939,7 +7085,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="C87">
         <v>1036</v>
@@ -7004,7 +7150,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="C88">
         <v>917</v>
@@ -7069,7 +7215,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="C89">
         <v>894</v>
@@ -7134,7 +7280,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="C90">
         <v>847</v>
@@ -7199,7 +7345,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="C91">
         <v>1042</v>
@@ -7264,7 +7410,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="C92">
         <v>1120</v>
@@ -7329,7 +7475,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="C93">
         <v>1137</v>
@@ -7394,7 +7540,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="C94">
         <v>898</v>
@@ -7459,7 +7605,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="C95">
         <v>877</v>
@@ -7524,7 +7670,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="C96">
         <v>1039</v>
@@ -7589,7 +7735,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="C97">
         <v>1143</v>
@@ -7654,7 +7800,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="C98">
         <v>1198</v>
@@ -7719,7 +7865,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="C99">
         <v>779</v>
@@ -7784,7 +7930,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="C100">
         <v>532</v>
@@ -7849,7 +7995,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="C101">
         <v>1052</v>
@@ -7914,7 +8060,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C102">
         <v>1051</v>
@@ -7979,7 +8125,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C103">
         <v>833</v>
@@ -8044,7 +8190,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C104">
         <v>1173</v>
@@ -8109,7 +8255,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C105">
         <v>835</v>
@@ -8174,7 +8320,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C106">
         <v>1147</v>
@@ -8239,7 +8385,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="C107">
         <v>857</v>
@@ -8304,7 +8450,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="C108">
         <v>855</v>
@@ -8369,7 +8515,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="C109">
         <v>1132</v>
@@ -8434,7 +8580,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="C110">
         <v>1102</v>
@@ -8499,7 +8645,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="C111">
         <v>959</v>
@@ -8564,7 +8710,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C112">
         <v>1030</v>
@@ -8629,7 +8775,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C113">
         <v>1137</v>
@@ -8694,7 +8840,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="C114">
         <v>778</v>
@@ -8759,7 +8905,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="C115">
         <v>636</v>
@@ -8824,7 +8970,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C116">
         <v>661</v>
@@ -8889,7 +9035,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="C117">
         <v>1004</v>
@@ -8954,7 +9100,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="C118">
         <v>614</v>
@@ -9019,7 +9165,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C119">
         <v>656</v>
@@ -9084,7 +9230,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="C120">
         <v>1144</v>
@@ -9149,7 +9295,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="C121">
         <v>595</v>
@@ -9214,7 +9360,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C122">
         <v>473</v>
@@ -9279,7 +9425,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C123">
         <v>631</v>
@@ -9344,7 +9490,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C124">
         <v>638</v>
@@ -9409,7 +9555,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="C125">
         <v>791</v>
@@ -9474,7 +9620,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="C126">
         <v>775</v>
@@ -9539,7 +9685,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="C127">
         <v>1112</v>
@@ -9604,7 +9750,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="C128">
         <v>1140</v>
@@ -9669,7 +9815,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="C129">
         <v>956</v>
@@ -9734,7 +9880,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C130">
         <v>1097</v>
@@ -9799,7 +9945,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="C131">
         <v>625</v>
@@ -9864,7 +10010,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="C132">
         <v>679</v>
@@ -9929,7 +10075,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C133">
         <v>1010</v>
@@ -9994,7 +10140,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="C134">
         <v>1079</v>
@@ -10059,7 +10205,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="C135">
         <v>1190</v>
@@ -10124,7 +10270,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="C136">
         <v>1083</v>
@@ -10189,7 +10335,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="C137">
         <v>637</v>
@@ -10254,7 +10400,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="C138">
         <v>1165</v>
@@ -10319,7 +10465,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="C139">
         <v>911</v>
@@ -10384,7 +10530,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="C140">
         <v>551</v>
@@ -10449,7 +10595,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="C141">
         <v>630</v>
@@ -10514,7 +10660,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="C142">
         <v>973</v>
@@ -10579,7 +10725,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C143">
         <v>860</v>
@@ -10644,7 +10790,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="C144">
         <v>1056</v>
@@ -10709,7 +10855,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="C145">
         <v>1078</v>
@@ -10774,7 +10920,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="C146">
         <v>1097</v>
@@ -10839,7 +10985,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="C147">
         <v>1110</v>
@@ -10904,7 +11050,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="C148">
         <v>826</v>
@@ -10969,7 +11115,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="C149">
         <v>796</v>
@@ -11034,7 +11180,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="C150">
         <v>871</v>
@@ -11099,7 +11245,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="C151">
         <v>1230</v>
@@ -11164,7 +11310,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="C152">
         <v>1246</v>
@@ -11229,7 +11375,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="C153">
         <v>1199</v>
@@ -11294,7 +11440,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="C154">
         <v>646</v>
@@ -11359,7 +11505,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="C155">
         <v>1246</v>
@@ -11424,7 +11570,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="C156">
         <v>1092</v>
@@ -11489,7 +11635,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="C157">
         <v>1019</v>
@@ -11554,7 +11700,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="C158">
         <v>1011</v>
@@ -11619,7 +11765,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="C159">
         <v>996</v>
@@ -11684,7 +11830,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="C160">
         <v>1017</v>
@@ -11749,7 +11895,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="C161">
         <v>937</v>
@@ -11814,7 +11960,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="C162">
         <v>690</v>
@@ -11879,7 +12025,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="C163">
         <v>1043</v>
@@ -11944,7 +12090,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="C164">
         <v>974</v>
@@ -12009,7 +12155,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="C165">
         <v>992</v>
@@ -12074,7 +12220,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="C166">
         <v>1231</v>
@@ -12139,7 +12285,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="C167">
         <v>1154</v>
@@ -12204,7 +12350,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="C168">
         <v>1123</v>
@@ -12269,7 +12415,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="C169">
         <v>1232</v>
@@ -12334,7 +12480,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="C170">
         <v>1211</v>
@@ -12399,7 +12545,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="C171">
         <v>941</v>
@@ -12464,7 +12610,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="C172">
         <v>958</v>
@@ -12529,7 +12675,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="C173">
         <v>756</v>
@@ -12594,7 +12740,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="C174">
         <v>1257</v>
@@ -12659,7 +12805,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="C175">
         <v>1252</v>
@@ -12724,7 +12870,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="C176">
         <v>1080</v>
@@ -12789,7 +12935,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="C177">
         <v>1095</v>
@@ -12854,7 +13000,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="C178">
         <v>689</v>
@@ -12919,7 +13065,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="C179">
         <v>914</v>
@@ -12984,7 +13130,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="C180">
         <v>1014</v>
@@ -13049,7 +13195,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="C181">
         <v>995</v>
@@ -13114,7 +13260,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="C182">
         <v>948</v>
@@ -13179,7 +13325,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="C183">
         <v>932</v>
@@ -13244,7 +13390,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="C184">
         <v>1139</v>
@@ -13309,7 +13455,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="C185">
         <v>822</v>
@@ -13374,7 +13520,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C186">
         <v>813</v>
@@ -13439,7 +13585,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="C187">
         <v>858</v>
@@ -13504,7 +13650,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="C188">
         <v>448</v>
@@ -13569,7 +13715,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="C189">
         <v>830</v>
@@ -13634,7 +13780,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="C190">
         <v>900</v>
@@ -13699,7 +13845,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="C191">
         <v>1028</v>
@@ -13764,7 +13910,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="C192">
         <v>767</v>
@@ -13829,7 +13975,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="C193">
         <v>825</v>
@@ -13894,7 +14040,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="C194">
         <v>1058</v>
@@ -13959,7 +14105,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="C195">
         <v>1183</v>
@@ -14024,7 +14170,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="C196">
         <v>1021</v>
@@ -14089,7 +14235,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="C197">
         <v>1023</v>
@@ -14154,7 +14300,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="C198">
         <v>1051</v>
@@ -14219,7 +14365,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="C199">
         <v>845</v>
@@ -14284,7 +14430,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C200">
         <v>1019</v>
@@ -14349,7 +14495,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="C201">
         <v>1035</v>
@@ -14414,7 +14560,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="C202">
         <v>1027</v>
@@ -14479,7 +14625,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="C203">
         <v>1001</v>
@@ -14544,7 +14690,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="C204">
         <v>1032</v>
@@ -14609,7 +14755,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="C205">
         <v>1074</v>
@@ -14674,7 +14820,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="C206">
         <v>1168</v>
@@ -14739,7 +14885,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="C207">
         <v>891</v>
@@ -14804,7 +14950,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="C208">
         <v>954</v>
@@ -14869,7 +15015,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="C209">
         <v>1037</v>
@@ -14934,7 +15080,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="C210">
         <v>1195</v>
@@ -14999,7 +15145,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="C211">
         <v>1087</v>
@@ -15064,7 +15210,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C212">
         <v>1146</v>
@@ -15129,7 +15275,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="C213">
         <v>947</v>
@@ -15194,7 +15340,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="C214">
         <v>1153</v>
@@ -15259,7 +15405,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="C215">
         <v>1154</v>
@@ -15324,7 +15470,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="C216">
         <v>1137</v>
@@ -15389,7 +15535,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="C217">
         <v>1104</v>
@@ -15454,7 +15600,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="C218">
         <v>1202</v>
@@ -15519,7 +15665,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="C219">
         <v>1204</v>
@@ -15584,7 +15730,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="C220">
         <v>1069</v>
@@ -15649,7 +15795,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="C221">
         <v>1102</v>
@@ -15714,7 +15860,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="C222">
         <v>947</v>
@@ -15779,7 +15925,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="C223">
         <v>1158</v>
@@ -15844,7 +15990,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="C224">
         <v>894</v>
@@ -15909,7 +16055,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="C225">
         <v>695</v>
@@ -15974,7 +16120,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -16039,7 +16185,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="C227">
         <v>1081</v>
@@ -16104,7 +16250,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="C228">
         <v>1002</v>
@@ -16169,7 +16315,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="C229">
         <v>938</v>
@@ -16234,7 +16380,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="C230">
         <v>920</v>
@@ -16299,7 +16445,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="C231">
         <v>808</v>
@@ -16364,7 +16510,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="C232">
         <v>1051</v>
@@ -16429,7 +16575,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="C233">
         <v>1144</v>
@@ -16494,7 +16640,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="C234">
         <v>868</v>
@@ -16559,7 +16705,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="C235">
         <v>919</v>
@@ -16624,7 +16770,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="C236">
         <v>732</v>
@@ -16689,7 +16835,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="C237">
         <v>1184</v>
@@ -16754,7 +16900,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="C238">
         <v>1187</v>
@@ -16819,7 +16965,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="C239">
         <v>1178</v>
@@ -16884,7 +17030,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="C240">
         <v>915</v>
@@ -16949,7 +17095,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="C241">
         <v>1043</v>
@@ -17014,7 +17160,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="C242">
         <v>1168</v>
@@ -17079,7 +17225,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="C243">
         <v>1128</v>
@@ -17144,7 +17290,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="C244">
         <v>1202</v>
@@ -17209,7 +17355,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="C245">
         <v>1167</v>
@@ -17274,7 +17420,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="C246">
         <v>1204</v>
@@ -17339,7 +17485,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C247">
         <v>1134</v>
@@ -17404,7 +17550,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="C248">
         <v>1143</v>
@@ -17469,7 +17615,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="C249">
         <v>1189</v>
@@ -17534,7 +17680,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="C250">
         <v>1090</v>
@@ -17599,7 +17745,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="C251">
         <v>1078</v>
@@ -17664,7 +17810,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="C252">
         <v>1171</v>
@@ -17729,7 +17875,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="C253">
         <v>960</v>
@@ -17794,7 +17940,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="C254">
         <v>984</v>
@@ -17859,7 +18005,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="C255">
         <v>936</v>
@@ -17924,7 +18070,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C256">
         <v>908</v>
@@ -17989,7 +18135,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="C257">
         <v>982</v>
@@ -18054,7 +18200,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="C258">
         <v>1137</v>
@@ -18119,7 +18265,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="C259">
         <v>1145</v>
@@ -18184,7 +18330,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="C260">
         <v>970</v>
@@ -18249,7 +18395,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="C261">
         <v>1190</v>
@@ -18314,7 +18460,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="C262">
         <v>1184</v>
@@ -18379,7 +18525,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="C263">
         <v>1043</v>
@@ -18444,7 +18590,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="C264">
         <v>957</v>
@@ -18509,7 +18655,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="C265">
         <v>1140</v>
@@ -18574,7 +18720,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="C266">
         <v>936</v>
@@ -18639,7 +18785,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="C267">
         <v>762</v>
@@ -18704,7 +18850,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="C268">
         <v>525</v>
@@ -18769,7 +18915,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="C269">
         <v>1210</v>
@@ -18834,7 +18980,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="C270">
         <v>1066</v>
@@ -18899,7 +19045,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="C271">
         <v>1140</v>
@@ -18964,7 +19110,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="C272">
         <v>1198</v>
@@ -19029,7 +19175,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="C273">
         <v>1071</v>
@@ -19094,7 +19240,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="C274">
         <v>1017</v>
@@ -19159,7 +19305,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="C275">
         <v>908</v>
@@ -19224,7 +19370,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="C276">
         <v>1088</v>
@@ -19289,7 +19435,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="C277">
         <v>1184</v>
@@ -19354,7 +19500,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="C278">
         <v>790</v>
@@ -19419,7 +19565,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="C279">
         <v>906</v>
@@ -19484,7 +19630,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="C280">
         <v>832</v>
@@ -19549,7 +19695,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="C281">
         <v>806</v>
@@ -19614,7 +19760,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="C282">
         <v>814</v>
@@ -19679,7 +19825,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="C283">
         <v>1182</v>
@@ -19744,7 +19890,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="C284">
         <v>1241</v>
@@ -19809,7 +19955,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="C285">
         <v>1004</v>
@@ -19874,7 +20020,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C286">
         <v>1140</v>
@@ -19939,7 +20085,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="C287">
         <v>888</v>
@@ -20004,7 +20150,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="C288">
         <v>953</v>
@@ -20069,7 +20215,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="C289">
         <v>1103</v>
@@ -20134,7 +20280,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="C290">
         <v>1016</v>
@@ -20199,7 +20345,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="C291">
         <v>1130</v>
@@ -20264,7 +20410,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="C292">
         <v>1187</v>
@@ -20329,7 +20475,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C293">
         <v>1222</v>
@@ -20394,7 +20540,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="C294">
         <v>1152</v>
@@ -20459,7 +20605,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="C295">
         <v>1118</v>
@@ -20524,7 +20670,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="C296">
         <v>1103</v>
@@ -20589,7 +20735,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="C297">
         <v>932</v>
@@ -20654,7 +20800,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="C298">
         <v>1069</v>
@@ -20719,7 +20865,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="C299">
         <v>1150</v>
@@ -20784,7 +20930,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="C300">
         <v>1091</v>
@@ -20849,7 +20995,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="C301">
         <v>1195</v>
@@ -20914,7 +21060,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="C302">
         <v>1149</v>
@@ -20979,7 +21125,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="C303">
         <v>1147</v>
@@ -21044,7 +21190,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="C304">
         <v>1147</v>
@@ -21109,7 +21255,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="C305">
         <v>1190</v>
@@ -21174,7 +21320,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="C306">
         <v>925</v>
@@ -21239,7 +21385,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="C307">
         <v>995</v>
@@ -21304,7 +21450,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="C308">
         <v>1090</v>
@@ -21369,7 +21515,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="C309">
         <v>1164</v>
@@ -21434,7 +21580,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="C310">
         <v>885</v>
@@ -21499,7 +21645,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="C311">
         <v>1164</v>
@@ -21564,7 +21710,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="C312">
         <v>1016</v>
@@ -21629,7 +21775,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="C313">
         <v>1117</v>
@@ -21694,7 +21840,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="C314">
         <v>1060</v>
@@ -21759,7 +21905,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="C315">
         <v>958</v>
@@ -21824,7 +21970,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="C316">
         <v>1037</v>
@@ -21889,7 +22035,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="C317">
         <v>1064</v>
@@ -21954,7 +22100,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="C318">
         <v>854</v>
@@ -22019,7 +22165,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="C319">
         <v>1060</v>
@@ -22084,7 +22230,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="C320">
         <v>1048</v>
@@ -22149,7 +22295,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="C321">
         <v>1000</v>
@@ -22214,7 +22360,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="C322">
         <v>1032</v>
@@ -22279,7 +22425,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="C323">
         <v>1013</v>
@@ -22344,7 +22490,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C324">
         <v>924</v>
@@ -22409,7 +22555,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="C325">
         <v>892</v>
@@ -22474,7 +22620,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="C326">
         <v>1163</v>
@@ -22539,7 +22685,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="C327">
         <v>1113</v>
@@ -22604,7 +22750,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="C328">
         <v>1186</v>
@@ -22669,7 +22815,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="C329">
         <v>1154</v>
@@ -22734,7 +22880,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="C330">
         <v>919</v>
@@ -22799,7 +22945,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="C331">
         <v>930</v>
@@ -22864,7 +23010,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="C332">
         <v>792</v>
@@ -22929,7 +23075,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="C333">
         <v>667</v>
@@ -22994,7 +23140,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="C334">
         <v>745</v>
@@ -23059,7 +23205,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="C335">
         <v>754</v>
@@ -23124,7 +23270,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="C336">
         <v>858</v>
@@ -23189,7 +23335,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="C337">
         <v>708</v>
@@ -23254,7 +23400,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="C338">
         <v>627</v>
